--- a/syllabus.xlsx
+++ b/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJSync\P&amp;J\Hebrew\YuchiClass\NewGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678527A6-406C-4EF2-80EE-3A40F0B35434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A0CF5E-452B-4E4D-BAC4-1505DD6D73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96EB7EBD-145B-4DF2-8E71-6858B4CD25ED}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>שלום אני פנוי</t>
   </si>
   <si>
-    <t>平安，我有空</t>
-  </si>
-  <si>
     <t>א</t>
   </si>
   <si>
@@ -313,24 +310,12 @@
     <t xml:space="preserve">אני רוצה קפה </t>
   </si>
   <si>
-    <t>我想 (m.) 喝咖啡</t>
-  </si>
-  <si>
     <t>אני אוהב אוֹתְךָ</t>
   </si>
   <si>
-    <t>我愛你 (m.)</t>
-  </si>
-  <si>
     <t>אתה רוצה קפה?</t>
   </si>
   <si>
-    <t>你想喝咖啡嗎？</t>
-  </si>
-  <si>
-    <t>妳想喝咖啡嗎？</t>
-  </si>
-  <si>
     <t>אני הוא לחם החיים</t>
   </si>
   <si>
@@ -346,15 +331,9 @@
     <t>אני רוצה לחם</t>
   </si>
   <si>
-    <t>我想要麵包</t>
-  </si>
-  <si>
     <t>אני צריך מים</t>
   </si>
   <si>
-    <t>我需要水</t>
-  </si>
-  <si>
     <t>אני צריכה מים</t>
   </si>
   <si>
@@ -364,39 +343,18 @@
     <t>אני צריך רופא</t>
   </si>
   <si>
-    <t>我需要醫生</t>
-  </si>
-  <si>
     <t>אתה צריך רופא</t>
   </si>
   <si>
-    <t>你需要醫生</t>
-  </si>
-  <si>
     <t>אתה צריך מים?</t>
   </si>
   <si>
-    <t>你需要水嗎？</t>
-  </si>
-  <si>
-    <t>妳需要食物嗎？</t>
-  </si>
-  <si>
-    <t>妳需要水嗎？</t>
-  </si>
-  <si>
     <t>אתה צריך אוכל?</t>
   </si>
   <si>
-    <t>你需要食物嗎？</t>
-  </si>
-  <si>
     <t>אני מאמין בְּיֵשׁוּעַ</t>
   </si>
   <si>
-    <t>我相信耶穌</t>
-  </si>
-  <si>
     <t>אני מאמינה בְּיֵשׁוּעַ</t>
   </si>
   <si>
@@ -406,21 +364,12 @@
     <t>אני אוהב אוֹתוֹ</t>
   </si>
   <si>
-    <t>我愛他</t>
-  </si>
-  <si>
     <t>אני אוהב אוֹתָהּ</t>
   </si>
   <si>
-    <t>我愛她</t>
-  </si>
-  <si>
     <t>平安！耶穌是道路、真理、生命。耶穌是生命的糧。他真偉大！我相信他，我也愛他。</t>
   </si>
   <si>
-    <t>אַת רוצה קפה?</t>
-  </si>
-  <si>
     <t>אתה פנוי?</t>
   </si>
   <si>
@@ -434,6 +383,57 @@
   </si>
   <si>
     <t>אַת צריכה מים?</t>
+  </si>
+  <si>
+    <t>אַת רוֹצָה קפה?</t>
+  </si>
+  <si>
+    <t>我 (m.) 想要麵包</t>
+  </si>
+  <si>
+    <t>我 (m.) 需要水</t>
+  </si>
+  <si>
+    <t>我 (m.) 需要醫生</t>
+  </si>
+  <si>
+    <t>我 (m.) 相信耶穌</t>
+  </si>
+  <si>
+    <t>妳 (f.) 需要食物嗎？</t>
+  </si>
+  <si>
+    <t>妳 (f.) 需要水嗎？</t>
+  </si>
+  <si>
+    <t>你 (m.) 需要醫生</t>
+  </si>
+  <si>
+    <t>你 (m.) 需要水嗎？</t>
+  </si>
+  <si>
+    <t>你 (m.) 需要食物嗎？</t>
+  </si>
+  <si>
+    <t>我 (m.) 愛他 (m.)</t>
+  </si>
+  <si>
+    <t>我 (m.) 愛她 (f.)</t>
+  </si>
+  <si>
+    <t>妳 (f.) 想喝咖啡嗎？</t>
+  </si>
+  <si>
+    <t>你 (m.) 想喝咖啡嗎？</t>
+  </si>
+  <si>
+    <t>我 (m.) 愛你 (m.)</t>
+  </si>
+  <si>
+    <t>我 (m.) 想喝咖啡</t>
+  </si>
+  <si>
+    <t>平安，我 (m.) 有空</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1410,7 @@
         <v>45886</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -1424,7 +1424,7 @@
         <v>45886</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1441,7 +1441,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1452,10 +1452,10 @@
         <v>45900</v>
       </c>
       <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
         <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1466,10 +1466,10 @@
         <v>45900</v>
       </c>
       <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1480,10 +1480,10 @@
         <v>45900</v>
       </c>
       <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
         <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1494,10 +1494,10 @@
         <v>45900</v>
       </c>
       <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1508,10 +1508,10 @@
         <v>45900</v>
       </c>
       <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
         <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1522,10 +1522,10 @@
         <v>45914</v>
       </c>
       <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
         <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1536,10 +1536,10 @@
         <v>45914</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
         <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1550,10 +1550,10 @@
         <v>45914</v>
       </c>
       <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
         <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1564,10 +1564,10 @@
         <v>45914</v>
       </c>
       <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
         <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1578,10 +1578,10 @@
         <v>45914</v>
       </c>
       <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
         <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1592,10 +1592,10 @@
         <v>45914</v>
       </c>
       <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
         <v>38</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1606,10 +1606,10 @@
         <v>45914</v>
       </c>
       <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
         <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1620,10 +1620,10 @@
         <v>45914</v>
       </c>
       <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
         <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1634,10 +1634,10 @@
         <v>45914</v>
       </c>
       <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
         <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1648,10 +1648,10 @@
         <v>45914</v>
       </c>
       <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
         <v>44</v>
-      </c>
-      <c r="D25" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1662,10 +1662,10 @@
         <v>45935</v>
       </c>
       <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
         <v>46</v>
-      </c>
-      <c r="D26" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1676,10 +1676,10 @@
         <v>45935</v>
       </c>
       <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
         <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1690,10 +1690,10 @@
         <v>45935</v>
       </c>
       <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
         <v>50</v>
-      </c>
-      <c r="D28" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1704,10 +1704,10 @@
         <v>45935</v>
       </c>
       <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
         <v>52</v>
-      </c>
-      <c r="D29" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1718,10 +1718,10 @@
         <v>45935</v>
       </c>
       <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
         <v>54</v>
-      </c>
-      <c r="D30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1732,10 +1732,10 @@
         <v>45935</v>
       </c>
       <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
         <v>56</v>
-      </c>
-      <c r="D31" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1746,10 +1746,10 @@
         <v>45935</v>
       </c>
       <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
         <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1760,10 +1760,10 @@
         <v>45935</v>
       </c>
       <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" t="s">
         <v>60</v>
-      </c>
-      <c r="D33" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1774,10 +1774,10 @@
         <v>45935</v>
       </c>
       <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" t="s">
         <v>62</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1788,10 +1788,10 @@
         <v>45935</v>
       </c>
       <c r="C35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" t="s">
         <v>64</v>
-      </c>
-      <c r="D35" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1802,10 +1802,10 @@
         <v>45935</v>
       </c>
       <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" t="s">
         <v>66</v>
-      </c>
-      <c r="D36" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1816,10 +1816,10 @@
         <v>45935</v>
       </c>
       <c r="C37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" t="s">
         <v>68</v>
-      </c>
-      <c r="D37" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1830,10 +1830,10 @@
         <v>45963</v>
       </c>
       <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
         <v>70</v>
-      </c>
-      <c r="D38" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1844,10 +1844,10 @@
         <v>45963</v>
       </c>
       <c r="C39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" t="s">
         <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1858,10 +1858,10 @@
         <v>45963</v>
       </c>
       <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
         <v>74</v>
-      </c>
-      <c r="D40" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1872,10 +1872,10 @@
         <v>45963</v>
       </c>
       <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
         <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1886,10 +1886,10 @@
         <v>45963</v>
       </c>
       <c r="C42" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" t="s">
         <v>78</v>
-      </c>
-      <c r="D42" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1900,10 +1900,10 @@
         <v>45963</v>
       </c>
       <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
         <v>80</v>
-      </c>
-      <c r="D43" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1914,10 +1914,10 @@
         <v>45963</v>
       </c>
       <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
         <v>82</v>
-      </c>
-      <c r="D44" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1928,10 +1928,10 @@
         <v>45963</v>
       </c>
       <c r="C45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
         <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1942,10 +1942,10 @@
         <v>46019</v>
       </c>
       <c r="C46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" t="s">
         <v>86</v>
-      </c>
-      <c r="D46" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1956,10 +1956,10 @@
         <v>46019</v>
       </c>
       <c r="C47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
         <v>88</v>
-      </c>
-      <c r="D47" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1970,10 +1970,10 @@
         <v>46019</v>
       </c>
       <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" t="s">
         <v>90</v>
-      </c>
-      <c r="D48" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1984,10 +1984,10 @@
         <v>46019</v>
       </c>
       <c r="C49" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" t="s">
         <v>92</v>
-      </c>
-      <c r="D49" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1998,10 +1998,10 @@
         <v>46019</v>
       </c>
       <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
         <v>94</v>
-      </c>
-      <c r="D50" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -2012,10 +2012,10 @@
         <v>46089</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2026,10 +2026,10 @@
         <v>46089</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2040,10 +2040,10 @@
         <v>46089</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2054,10 +2054,10 @@
         <v>46089</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2068,10 +2068,10 @@
         <v>46194</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2082,10 +2082,10 @@
         <v>46194</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2096,10 +2096,10 @@
         <v>46194</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2110,10 +2110,10 @@
         <v>46201</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2124,10 +2124,10 @@
         <v>46201</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2138,10 +2138,10 @@
         <v>46201</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -2152,10 +2152,10 @@
         <v>46201</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2166,10 +2166,10 @@
         <v>46201</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2180,10 +2180,10 @@
         <v>46201</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2194,10 +2194,10 @@
         <v>46201</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2208,10 +2208,10 @@
         <v>46201</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D65" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2222,10 +2222,10 @@
         <v>46208</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2236,10 +2236,10 @@
         <v>46208</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2250,10 +2250,10 @@
         <v>46215</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2264,10 +2264,10 @@
         <v>46215</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2278,10 +2278,10 @@
         <v>46215</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D70" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/syllabus.xlsx
+++ b/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJSync\P&amp;J\Hebrew\YuchiClass\NewGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A0CF5E-452B-4E4D-BAC4-1505DD6D73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFFECA9-FBAA-4088-AAC8-4BD9DDE6ACFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96EB7EBD-145B-4DF2-8E71-6858B4CD25ED}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
   <si>
     <t>Lesson</t>
   </si>
@@ -367,9 +367,6 @@
     <t>אני אוהב אוֹתָהּ</t>
   </si>
   <si>
-    <t>平安！耶穌是道路、真理、生命。耶穌是生命的糧。他真偉大！我相信他，我也愛他。</t>
-  </si>
-  <si>
     <t>אתה פנוי?</t>
   </si>
   <si>
@@ -434,6 +431,24 @@
   </si>
   <si>
     <t>平安，我 (m.) 有空</t>
+  </si>
+  <si>
+    <t>平安！耶穌是道路、真理、生命。耶穌是生命的糧。他真偉大！我 (m.) 相信他 (m.)，我 (m.) 也愛他 (m.)。</t>
+  </si>
+  <si>
+    <t>我 (f.) 愛他 (m.)</t>
+  </si>
+  <si>
+    <t>我 (f.) 愛她 (f.)</t>
+  </si>
+  <si>
+    <t>אני אוֹהֶבֶת אוֹתוֹ</t>
+  </si>
+  <si>
+    <t>אני אוֹהֶבֶת אוֹתָהּ</t>
+  </si>
+  <si>
+    <t>שלום! יֵשׁוּעַ הדרך והאמת והחיים. יֵשׁוּעַ לחם החיים. הוא גדול! אני מאמינה בו ואני אוֹהֶבֶת אוֹתוֹ.</t>
   </si>
 </sst>
 </file>
@@ -1296,11 +1311,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF4B01C-E855-4C1B-9D04-D8CDE07A667B}">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="69.77734375" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
     <col min="4" max="4" width="73.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1410,7 +1425,7 @@
         <v>45886</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -1424,7 +1439,7 @@
         <v>45886</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1441,7 +1456,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2015,7 +2030,7 @@
         <v>95</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2029,7 +2044,7 @@
         <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2043,7 +2058,7 @@
         <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2054,10 +2069,10 @@
         <v>46089</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2099,7 +2114,7 @@
         <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2113,7 +2128,7 @@
         <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2141,7 +2156,7 @@
         <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -2155,7 +2170,7 @@
         <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2169,7 +2184,7 @@
         <v>108</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2180,10 +2195,10 @@
         <v>46201</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2194,10 +2209,10 @@
         <v>46201</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2211,7 +2226,7 @@
         <v>109</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2225,7 +2240,7 @@
         <v>110</v>
       </c>
       <c r="D66" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2253,7 +2268,7 @@
         <v>113</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2267,21 +2282,54 @@
         <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>10</v>
-      </c>
       <c r="B70" s="1">
         <v>46215</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
-        <v>115</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B71" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C71" t="s">
+        <v>141</v>
+      </c>
+      <c r="D71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>10</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C72" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B73" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C73" t="s">
+        <v>142</v>
+      </c>
+      <c r="D73" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/syllabus.xlsx
+++ b/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJSync\P&amp;J\Hebrew\YuchiClass\NewGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFFECA9-FBAA-4088-AAC8-4BD9DDE6ACFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C65053-CC69-4072-A99E-CAF1B8BEEF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96EB7EBD-145B-4DF2-8E71-6858B4CD25ED}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="144">
   <si>
     <t>Lesson</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>שלום! יֵשׁוּעַ הדרך והאמת והחיים. יֵשׁוּעַ לחם החיים. הוא גדול! אני מאמינה בו ואני אוֹהֶבֶת אוֹתוֹ.</t>
+  </si>
+  <si>
+    <t>平安！耶穌是道路、真理、生命。耶穌是生命的糧。他真偉大！我 (f.) 相信他 (m.)，我 (f.) 也愛他 (m.)。</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2332,7 @@
         <v>142</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/syllabus.xlsx
+++ b/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJSync\P&amp;J\Hebrew\YuchiClass\NewGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C65053-CC69-4072-A99E-CAF1B8BEEF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE766740-666D-4407-B1C5-6A4B38AA8F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96EB7EBD-145B-4DF2-8E71-6858B4CD25ED}"/>
   </bookViews>
@@ -2289,6 +2289,9 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>10</v>
+      </c>
       <c r="B70" s="1">
         <v>46215</v>
       </c>
@@ -2300,6 +2303,9 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>10</v>
+      </c>
       <c r="B71" s="1">
         <v>46215</v>
       </c>
@@ -2325,6 +2331,9 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>10</v>
+      </c>
       <c r="B73" s="1">
         <v>46215</v>
       </c>

--- a/syllabus.xlsx
+++ b/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJSync\P&amp;J\Hebrew\YuchiClass\NewGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE766740-666D-4407-B1C5-6A4B38AA8F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0BAD99-C96F-46A5-B199-DDAD3A7FA330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96EB7EBD-145B-4DF2-8E71-6858B4CD25ED}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>מה העניינים? בסדר גמור! אתה בסדר?</t>
   </si>
   <si>
-    <t>你好嗎？很好！你OK嗎？</t>
-  </si>
-  <si>
     <t>חג חנוכה שָׂמֵחַ</t>
   </si>
   <si>
@@ -452,6 +449,9 @@
   </si>
   <si>
     <t>平安！耶穌是道路、真理、生命。耶穌是生命的糧。他真偉大！我 (f.) 相信他 (m.)，我 (f.) 也愛他 (m.)。</t>
+  </si>
+  <si>
+    <t>你好嗎？很好！你 (m.) OK嗎？</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1428,7 @@
         <v>45886</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -1442,7 +1442,7 @@
         <v>45886</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1459,7 +1459,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1991,7 +1991,7 @@
         <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -2002,10 +2002,10 @@
         <v>46019</v>
       </c>
       <c r="C49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" t="s">
         <v>91</v>
-      </c>
-      <c r="D49" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -2016,10 +2016,10 @@
         <v>46019</v>
       </c>
       <c r="C50" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" t="s">
         <v>93</v>
-      </c>
-      <c r="D50" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -2030,10 +2030,10 @@
         <v>46089</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -2044,10 +2044,10 @@
         <v>46089</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -2058,10 +2058,10 @@
         <v>46089</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -2072,10 +2072,10 @@
         <v>46089</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -2086,10 +2086,10 @@
         <v>46194</v>
       </c>
       <c r="C55" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" t="s">
         <v>98</v>
-      </c>
-      <c r="D55" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2100,10 +2100,10 @@
         <v>46194</v>
       </c>
       <c r="C56" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" t="s">
         <v>100</v>
-      </c>
-      <c r="D56" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -2114,10 +2114,10 @@
         <v>46194</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -2128,10 +2128,10 @@
         <v>46201</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -2142,10 +2142,10 @@
         <v>46201</v>
       </c>
       <c r="C59" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" t="s">
         <v>104</v>
-      </c>
-      <c r="D59" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -2156,10 +2156,10 @@
         <v>46201</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -2170,10 +2170,10 @@
         <v>46201</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -2184,10 +2184,10 @@
         <v>46201</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2198,10 +2198,10 @@
         <v>46201</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -2212,10 +2212,10 @@
         <v>46201</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2226,10 +2226,10 @@
         <v>46201</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -2240,10 +2240,10 @@
         <v>46208</v>
       </c>
       <c r="C66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2254,10 +2254,10 @@
         <v>46208</v>
       </c>
       <c r="C67" t="s">
+        <v>110</v>
+      </c>
+      <c r="D67" t="s">
         <v>111</v>
-      </c>
-      <c r="D67" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2268,10 +2268,10 @@
         <v>46215</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2282,10 +2282,10 @@
         <v>46215</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2296,10 +2296,10 @@
         <v>46215</v>
       </c>
       <c r="C70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2310,10 +2310,10 @@
         <v>46215</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2324,10 +2324,10 @@
         <v>46215</v>
       </c>
       <c r="C72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2338,10 +2338,10 @@
         <v>46215</v>
       </c>
       <c r="C73" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" t="s">
         <v>142</v>
-      </c>
-      <c r="D73" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
